--- a/public/assets/files/Excel_Demo-03/RECOLTE 2026/SISB_USEP_Stats.xlsx
+++ b/public/assets/files/Excel_Demo-03/RECOLTE 2026/SISB_USEP_Stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epflch-my.sharepoint.com/personal/genevieve_guex_epfl_ch/Documents/Documents/SISB_Presentations/SISB-Apero-Slidev/public/assets/files/Excel_Demo-03/RECOLTE 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1441" documentId="8_{B86F2B6C-3DE1-486D-B3D3-0A1863A11CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB568A99-AFC6-48EB-B822-C69C82F841B0}"/>
+  <xr:revisionPtr revIDLastSave="1457" documentId="8_{B86F2B6C-3DE1-486D-B3D3-0A1863A11CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2ECBDEF-627D-4995-B228-654B3C52F9F3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{537DF2C6-54A6-4649-8875-CD01F068054D}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="53">
   <si>
     <t>N° Indicateur</t>
   </si>
@@ -206,6 +206,9 @@
   </si>
   <si>
     <t>déc.26</t>
+  </si>
+  <si>
+    <t>Valeurs août et septembre</t>
   </si>
 </sst>
 </file>
@@ -271,12 +274,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39994506668294322"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39994506668294322"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39994506668294322"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39994506668294322"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -285,7 +303,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -342,6 +360,14 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
@@ -509,7 +535,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -618,54 +644,20 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -824,20 +816,54 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -887,7 +913,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -917,75 +943,126 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FE5B5D26-D6D4-45FE-9BEE-7E3541DA51DC}" name="TBL_USEP_2026" displayName="TBL_USEP_2026" ref="A1:P4" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34" headerRowCellStyle="Normal 2">
-  <autoFilter ref="A1:P4" xr:uid="{FE5B5D26-D6D4-45FE-9BEE-7E3541DA51DC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FE5B5D26-D6D4-45FE-9BEE-7E3541DA51DC}" name="TBL_USEP_2026" displayName="TBL_USEP_2026" ref="A1:P4" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52" headerRowCellStyle="Normal 2">
+  <autoFilter ref="A1:P4" xr:uid="{FE5B5D26-D6D4-45FE-9BEE-7E3541DA51DC}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+    <filterColumn colId="10" hiddenButton="1"/>
+    <filterColumn colId="11" hiddenButton="1"/>
+    <filterColumn colId="12" hiddenButton="1"/>
+    <filterColumn colId="13" hiddenButton="1"/>
+    <filterColumn colId="14" hiddenButton="1"/>
+    <filterColumn colId="15" hiddenButton="1"/>
+  </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{41BD5732-5556-4169-BA3E-70A38A7C7305}" name="N° Indicateur" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{D987DC9C-D5BD-4A34-9A43-8EAFCED0125E}" name="Équipe" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{545B44AE-DB69-4E69-B6CD-DB9EAB733F5A}" name="Indicateur" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{431406C4-32F3-458A-BF48-1D14D7B3D442}" name="Descriptif indicateur" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{82F2BF13-92F5-4FF4-AB8C-185145D618AD}" name="janv.26" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{A4068882-214D-4AAE-B2E0-49DEAAE648F7}" name="févr.26" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{CF274C19-1BB8-461C-8F1B-B51E236707AD}" name="mars26" dataDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{68763E8E-D0FA-4C54-AA16-ED7ED67C7ED3}" name="avr.26" dataDxfId="26"/>
-    <tableColumn id="9" xr3:uid="{D933F7F0-60A5-48E3-A231-B7D673FE66D8}" name="mai26" dataDxfId="25"/>
-    <tableColumn id="10" xr3:uid="{36BEC7F8-5F5F-4BC5-94DC-CA0DF4301B29}" name="juin26" dataDxfId="24"/>
-    <tableColumn id="11" xr3:uid="{B9534581-3166-4D17-A5EC-15C9DD012630}" name="juil.26" dataDxfId="23"/>
-    <tableColumn id="12" xr3:uid="{2211F4C9-0E9F-4E2E-8888-367FFF24D05F}" name="août26" dataDxfId="22"/>
-    <tableColumn id="13" xr3:uid="{45CD2345-B012-41DD-92E7-E9575B9AA733}" name="sept.26" dataDxfId="21"/>
-    <tableColumn id="14" xr3:uid="{A03AD678-42D2-4C5D-B349-AD1E0F1DDD72}" name="oct.26" dataDxfId="20"/>
-    <tableColumn id="15" xr3:uid="{F2FBD7B4-E7D9-4BD4-9AA5-944619803BE5}" name="nov.26" dataDxfId="19"/>
-    <tableColumn id="16" xr3:uid="{5FFC57C8-C568-4A1C-9A1C-6BBA48A28FC0}" name="déc.26" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{41BD5732-5556-4169-BA3E-70A38A7C7305}" name="N° Indicateur" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{D987DC9C-D5BD-4A34-9A43-8EAFCED0125E}" name="Équipe" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{545B44AE-DB69-4E69-B6CD-DB9EAB733F5A}" name="Indicateur" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{431406C4-32F3-458A-BF48-1D14D7B3D442}" name="Descriptif indicateur" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{82F2BF13-92F5-4FF4-AB8C-185145D618AD}" name="janv.26" dataDxfId="47"/>
+    <tableColumn id="6" xr3:uid="{A4068882-214D-4AAE-B2E0-49DEAAE648F7}" name="févr.26" dataDxfId="46"/>
+    <tableColumn id="7" xr3:uid="{CF274C19-1BB8-461C-8F1B-B51E236707AD}" name="mars26" dataDxfId="45"/>
+    <tableColumn id="8" xr3:uid="{68763E8E-D0FA-4C54-AA16-ED7ED67C7ED3}" name="avr.26" dataDxfId="44"/>
+    <tableColumn id="9" xr3:uid="{D933F7F0-60A5-48E3-A231-B7D673FE66D8}" name="mai26" dataDxfId="43"/>
+    <tableColumn id="10" xr3:uid="{36BEC7F8-5F5F-4BC5-94DC-CA0DF4301B29}" name="juin26" dataDxfId="42"/>
+    <tableColumn id="11" xr3:uid="{B9534581-3166-4D17-A5EC-15C9DD012630}" name="juil.26" dataDxfId="41"/>
+    <tableColumn id="12" xr3:uid="{2211F4C9-0E9F-4E2E-8888-367FFF24D05F}" name="août26" dataDxfId="40"/>
+    <tableColumn id="13" xr3:uid="{45CD2345-B012-41DD-92E7-E9575B9AA733}" name="sept.26" dataDxfId="39"/>
+    <tableColumn id="14" xr3:uid="{A03AD678-42D2-4C5D-B349-AD1E0F1DDD72}" name="oct.26" dataDxfId="38"/>
+    <tableColumn id="15" xr3:uid="{F2FBD7B4-E7D9-4BD4-9AA5-944619803BE5}" name="nov.26" dataDxfId="37"/>
+    <tableColumn id="16" xr3:uid="{5FFC57C8-C568-4A1C-9A1C-6BBA48A28FC0}" name="déc.26" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{62D8869E-0EB3-468A-9EAA-DA81846D2F2D}" name="TBL_USEP_2025" displayName="TBL_USEP_2025" ref="A1:P4" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16" headerRowCellStyle="Normal 2">
-  <autoFilter ref="A1:P4" xr:uid="{62D8869E-0EB3-468A-9EAA-DA81846D2F2D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{62D8869E-0EB3-468A-9EAA-DA81846D2F2D}" name="TBL_USEP_2025" displayName="TBL_USEP_2025" ref="A1:P4" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34" headerRowCellStyle="Normal 2">
+  <autoFilter ref="A1:P4" xr:uid="{62D8869E-0EB3-468A-9EAA-DA81846D2F2D}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+    <filterColumn colId="10" hiddenButton="1"/>
+    <filterColumn colId="11" hiddenButton="1"/>
+    <filterColumn colId="12" hiddenButton="1"/>
+    <filterColumn colId="13" hiddenButton="1"/>
+    <filterColumn colId="14" hiddenButton="1"/>
+    <filterColumn colId="15" hiddenButton="1"/>
+  </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{BE65C68B-1553-46D2-825A-ED7110D65F2B}" name="N° Indicateur" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{DDF081DC-85F0-45F1-90EA-7BF7506E52CA}" name="Équipe" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{EDD101BB-CCBC-43A3-8E70-1DB57EEA5001}" name="Indicateur" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{DB2002E4-9964-4C1E-B53B-71AE76E2FF90}" name="Descriptif indicateur" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{8F825606-5FC0-4E25-8D4F-54B08BB4F4F3}" name="janv.25" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{5CAE5512-8D1D-48FF-9772-A2ABC519CDAE}" name="févr.25" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{3BDD2626-AAA6-4DEC-AF6F-DBFC8783A7C5}" name="mars25" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{817E5857-4203-4ED8-B185-05DDB9521772}" name="avr.25" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{AD775858-CCD5-40F3-A9BF-721FA6582E5B}" name="mai25" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{ACAA387B-6286-40C0-AF7F-3A45B3CC8032}" name="juin25" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{108BB112-5793-4D64-A5C9-0D5B8B79436D}" name="juil.25" dataDxfId="5"/>
-    <tableColumn id="12" xr3:uid="{32817ED4-0D81-42FD-A8C4-C1BBBEEA744A}" name="août25" dataDxfId="4"/>
-    <tableColumn id="13" xr3:uid="{20EEFCD8-A569-4BFF-9CC8-1A1BFE8A8B60}" name="sept.25" dataDxfId="3"/>
-    <tableColumn id="14" xr3:uid="{E091E06E-DC4D-47B9-9F65-F30BC4BE136B}" name="oct.25" dataDxfId="2"/>
-    <tableColumn id="15" xr3:uid="{53DAC1AA-3282-4BCD-8CE9-C20F1CB18592}" name="nov.25" dataDxfId="1"/>
-    <tableColumn id="16" xr3:uid="{36E6877F-D0F2-42D1-B992-A932D2DA7B0A}" name="déc.25" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{BE65C68B-1553-46D2-825A-ED7110D65F2B}" name="N° Indicateur" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{DDF081DC-85F0-45F1-90EA-7BF7506E52CA}" name="Équipe" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{EDD101BB-CCBC-43A3-8E70-1DB57EEA5001}" name="Indicateur" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{DB2002E4-9964-4C1E-B53B-71AE76E2FF90}" name="Descriptif indicateur" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{8F825606-5FC0-4E25-8D4F-54B08BB4F4F3}" name="janv.25" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{5CAE5512-8D1D-48FF-9772-A2ABC519CDAE}" name="févr.25" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{3BDD2626-AAA6-4DEC-AF6F-DBFC8783A7C5}" name="mars25" dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{817E5857-4203-4ED8-B185-05DDB9521772}" name="avr.25" dataDxfId="26"/>
+    <tableColumn id="9" xr3:uid="{AD775858-CCD5-40F3-A9BF-721FA6582E5B}" name="mai25" dataDxfId="25"/>
+    <tableColumn id="10" xr3:uid="{ACAA387B-6286-40C0-AF7F-3A45B3CC8032}" name="juin25" dataDxfId="24"/>
+    <tableColumn id="11" xr3:uid="{108BB112-5793-4D64-A5C9-0D5B8B79436D}" name="juil.25" dataDxfId="23"/>
+    <tableColumn id="12" xr3:uid="{32817ED4-0D81-42FD-A8C4-C1BBBEEA744A}" name="août25" dataDxfId="22"/>
+    <tableColumn id="13" xr3:uid="{20EEFCD8-A569-4BFF-9CC8-1A1BFE8A8B60}" name="sept.25" dataDxfId="21"/>
+    <tableColumn id="14" xr3:uid="{E091E06E-DC4D-47B9-9F65-F30BC4BE136B}" name="oct.25" dataDxfId="20"/>
+    <tableColumn id="15" xr3:uid="{53DAC1AA-3282-4BCD-8CE9-C20F1CB18592}" name="nov.25" dataDxfId="19"/>
+    <tableColumn id="16" xr3:uid="{36E6877F-D0F2-42D1-B992-A932D2DA7B0A}" name="déc.25" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{ED97A496-1E9E-43D8-BC67-8369335930BA}" name="TBL_USEP_2024" displayName="TBL_USEP_2024" ref="A1:P4" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52" headerRowCellStyle="Normal 2">
-  <autoFilter ref="A1:P4" xr:uid="{ED97A496-1E9E-43D8-BC67-8369335930BA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{ED97A496-1E9E-43D8-BC67-8369335930BA}" name="TBL_USEP_2024" displayName="TBL_USEP_2024" ref="A1:P4" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16" headerRowCellStyle="Normal 2">
+  <autoFilter ref="A1:P4" xr:uid="{ED97A496-1E9E-43D8-BC67-8369335930BA}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+    <filterColumn colId="10" hiddenButton="1"/>
+    <filterColumn colId="11" hiddenButton="1"/>
+    <filterColumn colId="12" hiddenButton="1"/>
+    <filterColumn colId="13" hiddenButton="1"/>
+    <filterColumn colId="14" hiddenButton="1"/>
+    <filterColumn colId="15" hiddenButton="1"/>
+  </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{7BFA949C-0C3A-4157-A7ED-773618E82D8D}" name="N° Indicateur" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{7EA26EF2-E8C2-4EDC-99D2-459016BB4C38}" name="Équipe" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{D07B0472-9E43-4672-80D3-C842534E9C92}" name="Indicateur" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{5D2D5FBF-BBD3-44BD-9DA1-A41B91D9E7C9}" name="Descriptif indicateur" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{05D9ADF8-7855-46BC-9F8F-9491CFD343BE}" name="janv.24" dataDxfId="47"/>
-    <tableColumn id="6" xr3:uid="{0C60C792-AB40-49C0-A720-60732FCB8EFA}" name="févr.24" dataDxfId="46"/>
-    <tableColumn id="7" xr3:uid="{94D71EDB-31DF-455F-9613-FCA624176CD4}" name="mars24" dataDxfId="45"/>
-    <tableColumn id="8" xr3:uid="{DBC841BC-1FEF-405D-9226-B5B6ADEF50DD}" name="avr.24" dataDxfId="44"/>
-    <tableColumn id="9" xr3:uid="{786ABBD5-FCC4-4393-8CCF-64F95977E7C6}" name="mai24" dataDxfId="43"/>
-    <tableColumn id="10" xr3:uid="{A286FF83-A65A-45BC-8681-F23F82652D12}" name="juin24" dataDxfId="42"/>
-    <tableColumn id="11" xr3:uid="{6A65FDCB-3776-42DA-ABA0-1B3A7AEB9463}" name="juil.24" dataDxfId="41"/>
-    <tableColumn id="12" xr3:uid="{F760BD04-A40C-4FD7-9F9E-07482E53C4DD}" name="août24" dataDxfId="40"/>
-    <tableColumn id="13" xr3:uid="{2812A89A-E3AC-4814-904A-305CDDAF6D33}" name="sept.24" dataDxfId="39"/>
-    <tableColumn id="14" xr3:uid="{8C1A28E4-B68F-4845-BDDC-5117B0A52B2F}" name="oct.24" dataDxfId="38"/>
-    <tableColumn id="15" xr3:uid="{E0E87274-82F6-4DE3-9F17-E62A11743DCF}" name="nov.24" dataDxfId="37"/>
-    <tableColumn id="16" xr3:uid="{08E14BD8-46CF-4078-B442-FC4BA4C6FB3F}" name="déc.24" dataDxfId="36"/>
+    <tableColumn id="1" xr3:uid="{7BFA949C-0C3A-4157-A7ED-773618E82D8D}" name="N° Indicateur" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{7EA26EF2-E8C2-4EDC-99D2-459016BB4C38}" name="Équipe" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{D07B0472-9E43-4672-80D3-C842534E9C92}" name="Indicateur" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{5D2D5FBF-BBD3-44BD-9DA1-A41B91D9E7C9}" name="Descriptif indicateur" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{05D9ADF8-7855-46BC-9F8F-9491CFD343BE}" name="janv.24" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{0C60C792-AB40-49C0-A720-60732FCB8EFA}" name="févr.24" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{94D71EDB-31DF-455F-9613-FCA624176CD4}" name="mars24" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{DBC841BC-1FEF-405D-9226-B5B6ADEF50DD}" name="avr.24" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{786ABBD5-FCC4-4393-8CCF-64F95977E7C6}" name="mai24" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{A286FF83-A65A-45BC-8681-F23F82652D12}" name="juin24" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{6A65FDCB-3776-42DA-ABA0-1B3A7AEB9463}" name="juil.24" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{F760BD04-A40C-4FD7-9F9E-07482E53C4DD}" name="août24" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{2812A89A-E3AC-4814-904A-305CDDAF6D33}" name="sept.24" dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{8C1A28E4-B68F-4845-BDDC-5117B0A52B2F}" name="oct.24" dataDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{E0E87274-82F6-4DE3-9F17-E62A11743DCF}" name="nov.24" dataDxfId="1"/>
+    <tableColumn id="16" xr3:uid="{08E14BD8-46CF-4078-B442-FC4BA4C6FB3F}" name="déc.24" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1308,7 +1385,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3EA253C-11C5-4493-9357-287321BBEF02}">
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -1402,9 +1479,7 @@
       <c r="K2" s="10">
         <v>28845</v>
       </c>
-      <c r="L2" s="10">
-        <v>39741</v>
-      </c>
+      <c r="L2" s="10"/>
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
       <c r="O2" s="10"/>
@@ -1481,13 +1556,45 @@
       <c r="K4" s="13">
         <v>825</v>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="13"/>
+    </row>
+    <row r="19" spans="12:16" x14ac:dyDescent="0.2">
+      <c r="L19" s="23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="12:16" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="L21" s="20">
+        <v>39741</v>
+      </c>
+      <c r="M21" s="20">
+        <v>135291</v>
+      </c>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+    </row>
+    <row r="22" spans="12:16" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="L22" s="21"/>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+    </row>
+    <row r="23" spans="12:16" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="L23" s="22">
         <v>792</v>
       </c>
+      <c r="M23" s="22">
+        <v>1761</v>
+      </c>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation errorStyle="information" operator="greaterThan" showErrorMessage="1" errorTitle="Message SISB" error="Veuillez entrer un nombre positif entier" promptTitle="Message SISB" prompt="veuillez entrer un nombre entier" sqref="E4:L4 E2:P3" xr:uid="{A2B7FEED-18F0-4152-A24C-CA0BC5A6B90E}"/>
+    <dataValidation errorStyle="information" operator="greaterThan" showErrorMessage="1" errorTitle="Message SISB" error="Veuillez entrer un nombre positif entier" promptTitle="Message SISB" prompt="veuillez entrer un nombre entier" sqref="E4:L4 E2:P3 L21:P23" xr:uid="{A2B7FEED-18F0-4152-A24C-CA0BC5A6B90E}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
